--- a/previews/rapor.xlsx
+++ b/previews/rapor.xlsx
@@ -335,11 +335,6 @@
       </c>
     </row>
     <row>
-      <c s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ketidakhadiran</t>
-        </is>
-      </c>
       <c s="36">
         <v>4</v>
       </c>
@@ -348,11 +343,6 @@
           <t xml:space="preserve">Matematika</t>
         </is>
       </c>
-      <c s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Hari</t>
-        </is>
-      </c>
       <c s="36">
         <v>78</v>
       </c>
@@ -368,11 +358,6 @@
       </c>
     </row>
     <row>
-      <c s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sakit</t>
-        </is>
-      </c>
       <c s="34">
         <v>5</v>
       </c>
@@ -382,9 +367,6 @@
         </is>
       </c>
       <c s="34">
-        <v>2</v>
-      </c>
-      <c s="34">
         <v>85</v>
       </c>
       <c s="34" t="inlineStr">
@@ -399,16 +381,6 @@
       </c>
     </row>
     <row>
-      <c s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Izin</t>
-        </is>
-      </c>
-      <c s="34">
-        <v>1</v>
-      </c>
-    </row>
-    <row>
       <c s="36">
         <v>6</v>
       </c>
@@ -429,16 +401,6 @@
         <is>
           <t xml:space="preserve">Gambarnya penuh warna</t>
         </is>
-      </c>
-    </row>
-    <row>
-      <c s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tanpa keterangan</t>
-        </is>
-      </c>
-      <c s="34">
-        <v>0</v>
       </c>
     </row>
     <row>
@@ -508,6 +470,16 @@
       </c>
     </row>
     <row>
+      <c s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ketidakhadiran</t>
+        </is>
+      </c>
+      <c s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hari</t>
+        </is>
+      </c>
       <c s="40" t="inlineStr">
         <is>
           <t xml:space="preserve">Catatan wali kelas</t>
@@ -515,10 +487,38 @@
       </c>
     </row>
     <row>
+      <c s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sakit</t>
+        </is>
+      </c>
+      <c s="34">
+        <v>2</v>
+      </c>
       <c s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Aisyah rajin bertanya dan senang membantu teman. Pertahankan semangat membacanya, dan terus berlatih perkalian di rumah ya!</t>
         </is>
+      </c>
+    </row>
+    <row>
+      <c s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izin</t>
+        </is>
+      </c>
+      <c s="34">
+        <v>1</v>
+      </c>
+    </row>
+    <row>
+      <c s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tanpa keterangan</t>
+        </is>
+      </c>
+      <c s="34">
+        <v>0</v>
       </c>
     </row>
     <row>
